--- a/questionnaire_templates/022_eye_and_ear_infection_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/022_eye_and_ear_infection_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -910,29 +910,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eye_pain</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eye pain</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eye_infection_symptoms_choices</t>
+          <t>contact_with_another_person_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Redness</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -944,29 +944,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contact_with_another_person_choices</t>
+          <t>contact_with_another_person_eye_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -978,29 +978,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_with_another_person_eye_choices</t>
+          <t>medical_history_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1012,29 +1012,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_eye_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>medical_history_eye_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>True</t>
         </is>
